--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486710_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486710_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4009</v>
+        <v>1.6536</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5922</v>
+        <v>1.82</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1913</v>
+        <v>-0.1665</v>
       </c>
       <c r="G2" t="n">
         <v>2.088</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5406</v>
+        <v>-0.2068</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6616</v>
+        <v>-0.1106</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.121</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6138</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>J. HERRERO ALONSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1985</v>
+        <v>0.7611</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2207</v>
+        <v>0.3061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4193</v>
+        <v>0.4549</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1379</v>
+        <v>-0.1233</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0.8898</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1379</v>
+        <v>0.7665</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2.2369</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.1456</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.0913</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1379</v>
+        <v>-2.3602</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.0354</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1379</v>
+        <v>-1.3248</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3862</v>
+        <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3255</v>
+        <v>-0.4552</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2207</v>
+        <v>-0.5246</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1048</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.498</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HERRERO ALONSO</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4388</v>
+        <v>0.3516</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5213</v>
+        <v>-0.1173</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0825</v>
+        <v>0.4689</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1233</v>
+        <v>0.1379</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8898</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7665</v>
+        <v>0.1379</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2369</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1456</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0913</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3602</v>
+        <v>0.1379</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0354</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3248</v>
+        <v>0.1379</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7031</v>
+        <v>0.3862</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.655</v>
+        <v>-0.1724</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.352</v>
+        <v>-0.1173</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.303</v>
+        <v>-0.0551</v>
       </c>
       <c r="V4" t="n">
-        <v>2.498</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4676</v>
+        <v>-0.0829</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8275</v>
+        <v>-0.5172</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3599</v>
+        <v>0.4344</v>
       </c>
       <c r="G5" t="n">
         <v>0.1999</v>
@@ -844,13 +844,13 @@
         <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2814</v>
+        <v>0.1033</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1932</v>
+        <v>0.1171</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0882</v>
+        <v>-0.0137</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.8562</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0219</v>
+        <v>-2.277</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4953</v>
+        <v>1.4208</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9129</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2703</v>
+        <v>-0.5999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1925</v>
+        <v>-0.0626</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4628</v>
+        <v>-0.5373</v>
       </c>
       <c r="V6" t="n">
         <v>0.6565</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9274</v>
+        <v>-1.4212</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.8216</v>
+        <v>-3.663</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8941</v>
+        <v>2.2418</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7123</v>
@@ -1000,13 +1000,13 @@
         <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4509</v>
+        <v>-0.9446</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9933</v>
+        <v>-0.8347</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4576</v>
+        <v>-0.1099</v>
       </c>
       <c r="V7" t="n">
         <v>0.6565</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7903</v>
+        <v>-2.9641</v>
       </c>
       <c r="E8" t="n">
         <v>-2.3559</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4344</v>
+        <v>-0.6082</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0473</v>
@@ -1078,13 +1078,13 @@
         <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3914</v>
+        <v>-0.5653</v>
       </c>
       <c r="T8" t="n">
         <v>-0.4142</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0227</v>
+        <v>-0.1511</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. LUIS HERRERA</t>
+          <t>E. AMANDIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0027</v>
+        <v>-3.9166</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.988</v>
+        <v>-2.2046</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0147</v>
+        <v>-1.712</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.575</v>
+        <v>-1.6819</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2276</v>
+        <v>0.4838</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3474</v>
+        <v>-2.1657</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4499</v>
+        <v>0.1267</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.572</v>
+        <v>1.3813</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>-1.2546</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1251</v>
+        <v>-1.8086</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3443</v>
+        <v>-0.8975</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4695</v>
+        <v>-0.9111</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7377</v>
+        <v>2.7031</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1862</v>
+        <v>-0.5516</v>
       </c>
       <c r="T9" t="n">
-        <v>0.358</v>
+        <v>-0.4005</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8280999999999999</v>
+        <v>-0.1511</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4554</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. AMANDIO</t>
+          <t>N. LUIS HERRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0048</v>
+        <v>-5.0372</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4666</v>
+        <v>-3.4017</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5382</v>
+        <v>-1.6355</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6819</v>
+        <v>-1.575</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4838</v>
+        <v>-0.2276</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1657</v>
+        <v>-1.3474</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1267</v>
+        <v>-0.4499</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3813</v>
+        <v>-0.572</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2546</v>
+        <v>0.1221</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8086</v>
+        <v>-1.1251</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8975</v>
+        <v>0.3443</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9111</v>
+        <v>-1.4695</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7723</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7031</v>
+        <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6398</v>
+        <v>0.1517</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6625</v>
+        <v>-0.0557</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0227</v>
+        <v>0.2073</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4554</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8089</v>
+        <v>-5.5799</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.476</v>
+        <v>-6.4208</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6671</v>
+        <v>0.8409</v>
       </c>
       <c r="G11" t="n">
         <v>-3.856</v>
@@ -1312,13 +1312,13 @@
         <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9875</v>
+        <v>-0.7585</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5518</v>
+        <v>-0.4966</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4357</v>
+        <v>-0.2619</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-17.3678</v>
+        <v>-17.0918</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.1073</v>
+        <v>-18.8314</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7396</v>
+        <v>1.7395</v>
       </c>
       <c r="G12" t="n">
         <v>-8.482900000000001</v>
@@ -1360,13 +1360,13 @@
         <v>-2.4128</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.07</v>
+        <v>-6.070000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>-1.8862</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3381000000000003</v>
+        <v>-0.3380999999999998</v>
       </c>
       <c r="L12" t="n">
         <v>-1.5481</v>
@@ -1378,7 +1378,7 @@
         <v>-2.0748</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.521800000000001</v>
+        <v>-4.5218</v>
       </c>
       <c r="P12" t="n">
         <v>-2.8962</v>
@@ -1390,13 +1390,13 @@
         <v>15.4462</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.275</v>
+        <v>-3.9993</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.1756</v>
+        <v>-2.8997</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0996</v>
+        <v>-1.0995</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7136</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.9208</v>
+        <v>8.7537</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7966</v>
+        <v>6.4171</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1242</v>
+        <v>2.3366</v>
       </c>
       <c r="G13" t="n">
         <v>8.050000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>2.3169</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7776999999999999</v>
+        <v>0.0552</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8279</v>
+        <v>-0.2073</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0501</v>
+        <v>0.2625</v>
       </c>
       <c r="V13" t="n">
         <v>1.2277</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.6268</v>
+        <v>5.9952</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3273</v>
+        <v>3.7068</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2995</v>
+        <v>2.2884</v>
       </c>
       <c r="G14" t="n">
         <v>5.8325</v>
@@ -1546,13 +1546,13 @@
         <v>2.3169</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7211</v>
+        <v>1.0895</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2131</v>
+        <v>0.5925</v>
       </c>
       <c r="U14" t="n">
-        <v>0.508</v>
+        <v>0.4969</v>
       </c>
       <c r="V14" t="n">
         <v>-1.3129</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.249</v>
+        <v>5.3095</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4488</v>
+        <v>3.1727</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8003</v>
+        <v>2.1368</v>
       </c>
       <c r="G15" t="n">
         <v>1.8683</v>
@@ -1624,13 +1624,13 @@
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7778</v>
+        <v>0.2827</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2258</v>
+        <v>0.1107</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1289</v>
+        <v>1.5715</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0001</v>
+        <v>-0.483</v>
       </c>
       <c r="F16" t="n">
-        <v>2.129</v>
+        <v>2.0545</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3661</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1434</v>
+        <v>0.586</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6898</v>
+        <v>-0.1727</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.7588</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9052</v>
+        <v>1.0922</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1336</v>
+        <v>-3.1687</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7716</v>
+        <v>4.2609</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4239</v>
+        <v>-0.5061</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4759</v>
+        <v>0.8547</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.052</v>
+        <v>-1.3609</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7489</v>
+        <v>-1.5532</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5454</v>
+        <v>0.5107</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2035</v>
+        <v>-2.0639</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.325</v>
+        <v>1.047</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06950000000000001</v>
+        <v>0.344</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2555</v>
+        <v>0.703</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9654</v>
+        <v>2.7031</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7983</v>
+        <v>0.5171</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7097</v>
+        <v>0.0063</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0886</v>
+        <v>0.5107</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6138</v>
+        <v>-0.6565</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5712</v>
+        <v>-0.6565</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. BOONYASITH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7571</v>
+        <v>0.1192</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.479</v>
+        <v>-2.342</v>
       </c>
       <c r="F18" t="n">
-        <v>4.236</v>
+        <v>2.4613</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5061</v>
+        <v>-0.2534</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8547</v>
+        <v>0.1106</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3609</v>
+        <v>-0.3639</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5532</v>
+        <v>-0.3974</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5107</v>
+        <v>0.2491</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0639</v>
+        <v>-0.6465</v>
       </c>
       <c r="M18" t="n">
-        <v>1.047</v>
+        <v>0.144</v>
       </c>
       <c r="N18" t="n">
-        <v>0.344</v>
+        <v>-0.1385</v>
       </c>
       <c r="O18" t="n">
-        <v>0.703</v>
+        <v>0.2826</v>
       </c>
       <c r="P18" t="n">
+        <v>-1.1585</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2.8962</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.7377</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.7031</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.182</v>
+        <v>0.3034</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3039</v>
+        <v>-0.2761</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4859</v>
+        <v>0.5795</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6565</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BOONYASITH</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1455</v>
+        <v>-0.2724</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7557</v>
+        <v>-1.1074</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6103</v>
+        <v>0.835</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2534</v>
+        <v>0.4239</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1106</v>
+        <v>0.4759</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3639</v>
+        <v>-0.052</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3974</v>
+        <v>0.7489</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2491</v>
+        <v>0.5454</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6465</v>
+        <v>0.2035</v>
       </c>
       <c r="M19" t="n">
-        <v>0.144</v>
+        <v>-0.325</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1385</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2826</v>
+        <v>-0.2555</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1585</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.8962</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0387</v>
+        <v>0.6206</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6898</v>
+        <v>0.4686</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7285</v>
+        <v>0.152</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2277</v>
+        <v>0.5712</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>F. NAVARRO ANTON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4198</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9694</v>
+        <v>-0.704</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5496</v>
+        <v>0.1793</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6939</v>
+        <v>-0.5109</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5794</v>
+        <v>0.1379</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1145</v>
+        <v>-0.6488</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1621</v>
+        <v>-0.6488</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7168</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4453</v>
+        <v>-0.6488</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5318000000000001</v>
+        <v>0.1379</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1374</v>
+        <v>0.1379</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6692</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2741</v>
+        <v>-0.0138</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1581</v>
+        <v>-0.0552</v>
       </c>
       <c r="U20" t="n">
-        <v>0.116</v>
+        <v>0.0414</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. NAVARRO ANTON</t>
+          <t>M. OLIVA I CAMPABADAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5495</v>
+        <v>-0.87</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.704</v>
+        <v>-1.0898</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1545</v>
+        <v>0.2198</v>
       </c>
       <c r="G21" t="n">
+        <v>-1.0214</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5105</v>
+      </c>
+      <c r="I21" t="n">
         <v>-0.5109</v>
       </c>
-      <c r="H21" t="n">
-        <v>0.1379</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-0.6488</v>
-      </c>
       <c r="J21" t="n">
-        <v>-0.6488</v>
+        <v>-1.5725</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.2343</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6488</v>
+        <v>-1.3383</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1379</v>
+        <v>0.5511</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1379</v>
+        <v>-0.2763</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.8274</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0386</v>
+        <v>0.7998</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0552</v>
+        <v>0.2204</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0166</v>
+        <v>0.5795</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. OLIVA I CAMPABADAL</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-1.0733</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0898</v>
+        <v>-1.7968</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3192</v>
+        <v>0.7235</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0214</v>
+        <v>-1.6939</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5105</v>
+        <v>-0.5794</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5109</v>
+        <v>-1.1145</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5725</v>
+        <v>-1.1621</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2343</v>
+        <v>-0.7168</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3383</v>
+        <v>-0.4453</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5511</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2763</v>
+        <v>0.1374</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8274</v>
+        <v>-0.6692</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8992</v>
+        <v>0.6206</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2204</v>
+        <v>0.3307</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6788</v>
+        <v>0.2898</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3346</v>
+        <v>-2.0436</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.1043</v>
+        <v>-5.0009</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7697</v>
+        <v>2.9573</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3402</v>
@@ -2248,13 +2248,13 @@
         <v>2.51</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1875</v>
+        <v>0.1035</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0832</v>
+        <v>0.0202</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1043</v>
+        <v>0.0832</v>
       </c>
       <c r="V23" t="n">
         <v>0.6138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>17.3677</v>
+        <v>18.0573</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.396000000000002</v>
+        <v>-2.396000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>19.7639</v>
+        <v>20.4534</v>
       </c>
       <c r="G24" t="n">
         <v>8.482700000000001</v>
@@ -2299,7 +2299,7 @@
         <v>6.070000000000002</v>
       </c>
       <c r="J24" t="n">
-        <v>6.5966</v>
+        <v>6.596599999999999</v>
       </c>
       <c r="K24" t="n">
         <v>2.074599999999999</v>
@@ -2311,7 +2311,7 @@
         <v>1.886</v>
       </c>
       <c r="N24" t="n">
-        <v>0.338</v>
+        <v>0.3379999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>1.5481</v>
@@ -2326,13 +2326,13 @@
         <v>18.3423</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2752</v>
+        <v>4.964600000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0996</v>
+        <v>1.0994</v>
       </c>
       <c r="U24" t="n">
-        <v>3.1756</v>
+        <v>3.865000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>1.7136</v>
